--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121338933</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121338957</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>121338905</v>
       </c>
       <c r="B4" t="n">
-        <v>91302</v>
+        <v>91312</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121338957</v>
+        <v>121338905</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>91312</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,50 +802,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 53075, Pjäkebo, Sm</t>
+          <t>A 52992, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569741</v>
+        <v>569435</v>
       </c>
       <c r="R3" t="n">
-        <v>6435696</v>
+        <v>6435614</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,12 +879,18 @@
           <t>2024-11-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121338905</v>
+        <v>121338957</v>
       </c>
       <c r="B4" t="n">
-        <v>91312</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,49 +921,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 52992, Pjäkebo, Sm</t>
+          <t>A 53075, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569435</v>
+        <v>569741</v>
       </c>
       <c r="R4" t="n">
-        <v>6435614</v>
+        <v>6435696</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,18 +999,12 @@
           <t>2024-11-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>121338905</v>
       </c>
       <c r="B3" t="n">
-        <v>91312</v>
+        <v>91324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121338933</v>
+        <v>121338957</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 52992, Pjäkebo, Sm</t>
+          <t>A 53075, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569484</v>
+        <v>569741</v>
       </c>
       <c r="R2" t="n">
-        <v>6435567</v>
+        <v>6435696</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +792,7 @@
         <v>121338905</v>
       </c>
       <c r="B3" t="n">
-        <v>91324</v>
+        <v>91325</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121338957</v>
+        <v>121338933</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,49 +924,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 53075, Pjäkebo, Sm</t>
+          <t>A 52992, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569741</v>
+        <v>569484</v>
       </c>
       <c r="R4" t="n">
-        <v>6435696</v>
+        <v>6435567</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,6 +992,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121338957</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121338905</v>
       </c>
       <c r="B3" t="n">
-        <v>91325</v>
+        <v>91328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>121338933</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121338957</v>
+        <v>121338905</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>91328</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 53075, Pjäkebo, Sm</t>
+          <t>A 52992, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569741</v>
+        <v>569435</v>
       </c>
       <c r="R2" t="n">
-        <v>6435696</v>
+        <v>6435614</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,12 +764,18 @@
           <t>2024-11-25</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121338905</v>
+        <v>121338933</v>
       </c>
       <c r="B3" t="n">
-        <v>91328</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +806,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569435</v>
+        <v>569484</v>
       </c>
       <c r="R3" t="n">
-        <v>6435614</v>
+        <v>6435567</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121338933</v>
+        <v>121338957</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,45 +925,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 52992, Pjäkebo, Sm</t>
+          <t>A 53075, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569484</v>
+        <v>569741</v>
       </c>
       <c r="R4" t="n">
-        <v>6435567</v>
+        <v>6435696</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,11 +997,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121338905</v>
+        <v>121338957</v>
       </c>
       <c r="B2" t="n">
-        <v>91328</v>
+        <v>57508</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 52992, Pjäkebo, Sm</t>
+          <t>A 53075, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569435</v>
+        <v>569741</v>
       </c>
       <c r="R2" t="n">
-        <v>6435614</v>
+        <v>6435696</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,18 +765,12 @@
           <t>2024-11-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,7 +792,7 @@
         <v>121338933</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121338957</v>
+        <v>121338905</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>91334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,50 +916,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 53075, Pjäkebo, Sm</t>
+          <t>A 52992, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569741</v>
+        <v>569435</v>
       </c>
       <c r="R4" t="n">
-        <v>6435696</v>
+        <v>6435614</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -999,12 +993,18 @@
           <t>2024-11-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121338957</v>
       </c>
       <c r="B2" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121338933</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>121338905</v>
       </c>
       <c r="B4" t="n">
-        <v>91334</v>
+        <v>91335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121338933</v>
+        <v>121338905</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>91335</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569484</v>
+        <v>569435</v>
       </c>
       <c r="R3" t="n">
-        <v>6435567</v>
+        <v>6435614</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bearbetat låga</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121338905</v>
+        <v>121338933</v>
       </c>
       <c r="B4" t="n">
-        <v>91335</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +920,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569435</v>
+        <v>569484</v>
       </c>
       <c r="R4" t="n">
-        <v>6435614</v>
+        <v>6435567</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +996,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1005,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121338957</v>
+        <v>121338933</v>
       </c>
       <c r="B2" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 53075, Pjäkebo, Sm</t>
+          <t>A 52992, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569741</v>
+        <v>569484</v>
       </c>
       <c r="R2" t="n">
-        <v>6435696</v>
+        <v>6435567</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -908,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121338933</v>
+        <v>121338957</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,45 +925,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 52992, Pjäkebo, Sm</t>
+          <t>A 53075, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569484</v>
+        <v>569741</v>
       </c>
       <c r="R4" t="n">
-        <v>6435567</v>
+        <v>6435696</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,11 +997,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121338933</v>
+        <v>121338957</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 52992, Pjäkebo, Sm</t>
+          <t>A 53075, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569484</v>
+        <v>569741</v>
       </c>
       <c r="R2" t="n">
-        <v>6435567</v>
+        <v>6435696</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -909,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121338957</v>
+        <v>121338933</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,49 +924,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 53075, Pjäkebo, Sm</t>
+          <t>A 52992, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569741</v>
+        <v>569484</v>
       </c>
       <c r="R4" t="n">
-        <v>6435696</v>
+        <v>6435567</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,6 +992,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121338957</v>
       </c>
       <c r="B2" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121338905</v>
+        <v>121338933</v>
       </c>
       <c r="B3" t="n">
-        <v>91335</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569435</v>
+        <v>569484</v>
       </c>
       <c r="R3" t="n">
-        <v>6435614</v>
+        <v>6435567</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +877,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121338933</v>
+        <v>121338905</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>91343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,35 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569484</v>
+        <v>569435</v>
       </c>
       <c r="R4" t="n">
-        <v>6435567</v>
+        <v>6435614</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bearbetat låga</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +1004,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52992-2024 artfynd.xlsx
+++ b/artfynd/A 52992-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121338957</v>
+        <v>121338905</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 53075, Pjäkebo, Sm</t>
+          <t>A 52992, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569741</v>
+        <v>569435</v>
       </c>
       <c r="R2" t="n">
-        <v>6435696</v>
+        <v>6435614</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,12 +759,18 @@
           <t>2024-11-25</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,16 +792,11 @@
         <v>121338933</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -904,61 +899,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121338905</v>
+        <v>121338944</v>
       </c>
       <c r="B4" t="n">
-        <v>91343</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 52992, Pjäkebo, Sm</t>
+          <t>A 53075, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569435</v>
+        <v>569628</v>
       </c>
       <c r="R4" t="n">
-        <v>6435614</v>
+        <v>6435776</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,18 +984,12 @@
           <t>2024-11-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,6 +1005,115 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121338957</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 53075, Pjäkebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>569741</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6435696</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
